--- a/姜博文爬虫自查结果.xlsx
+++ b/姜博文爬虫自查结果.xlsx
@@ -3449,7 +3449,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3476,13 +3476,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -3519,6 +3512,25 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -4013,28 +4025,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4043,122 +4046,131 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4169,39 +4181,54 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -10027,31 +10054,33 @@
       <c r="A175" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="B175" s="12">
+      <c r="B175" s="16">
         <v>1960</v>
       </c>
-      <c r="C175" s="13" t="s">
+      <c r="C175" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="D175" s="12">
+      <c r="D175" s="16">
         <v>4</v>
       </c>
-      <c r="E175" s="12">
+      <c r="E175" s="16">
         <v>2</v>
       </c>
-      <c r="F175" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="G175" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H175" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I175" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J175" s="15" t="s">
+      <c r="F175" s="18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:（光緒）永昌府志_-_光緒十一年_(1885).pdf</t>
+        </is>
+      </c>
+      <c r="G175" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H175" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J175" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -10152,98 +10181,104 @@
       </c>
     </row>
     <row r="179" ht="72.5" spans="1:10">
-      <c r="A179" s="11" t="s">
+      <c r="A179" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B179" s="12">
+      <c r="B179" s="16">
         <v>2474</v>
       </c>
-      <c r="C179" s="13" t="s">
+      <c r="C179" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="D179" s="12">
+      <c r="D179" s="16">
         <v>5</v>
       </c>
-      <c r="E179" s="12">
+      <c r="E179" s="16">
         <v>3</v>
       </c>
-      <c r="F179" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="G179" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H179" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I179" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J179" s="15" t="s">
+      <c r="F179" s="18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:CADAL02090185_約章成案匯覽（三十七）.djvu</t>
+        </is>
+      </c>
+      <c r="G179" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H179" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J179" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="180" ht="377" spans="1:10">
-      <c r="A180" s="11" t="s">
+      <c r="A180" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B180" s="12">
+      <c r="B180" s="16">
         <v>2604</v>
       </c>
-      <c r="C180" s="13" t="s">
+      <c r="C180" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="D180" s="12">
+      <c r="D180" s="16">
         <v>5</v>
       </c>
-      <c r="E180" s="12">
+      <c r="E180" s="16">
         <v>3</v>
       </c>
-      <c r="F180" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="G180" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H180" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I180" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J180" s="15" t="s">
+      <c r="F180" s="18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:（光緒）嘉興縣志_-_光緒三十四年_(1908)_-_卷00-16.pdf</t>
+        </is>
+      </c>
+      <c r="G180" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H180" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J180" s="19" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="181" ht="362.5" spans="1:10">
-      <c r="A181" s="11" t="s">
+      <c r="A181" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B181" s="12">
+      <c r="B181" s="16">
         <v>2733</v>
       </c>
-      <c r="C181" s="13" t="s">
+      <c r="C181" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D181" s="12">
+      <c r="D181" s="16">
         <v>5</v>
       </c>
-      <c r="E181" s="12">
+      <c r="E181" s="16">
         <v>3</v>
       </c>
-      <c r="F181" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="G181" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H181" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I181" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J181" s="15" t="s">
+      <c r="F181" s="18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:（康熙）汾西縣志_-_康熙十三年_(1674).pdf</t>
+        </is>
+      </c>
+      <c r="G181" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H181" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J181" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -11304,34 +11339,37 @@
       </c>
     </row>
     <row r="215" ht="304.5" spans="1:10">
-      <c r="A215" s="11" t="s">
+      <c r="A215" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B215" s="12">
+      <c r="B215" s="16">
         <v>7092</v>
       </c>
-      <c r="C215" s="13" t="s">
+      <c r="C215" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="D215" s="12">
+      <c r="D215" s="16">
         <v>12</v>
       </c>
-      <c r="E215" s="12">
+      <c r="E215" s="16">
         <v>3</v>
       </c>
-      <c r="F215" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="G215" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H215" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I215" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J215" s="15" t="s">
+      <c r="F215" s="18" t="inlineStr">
+        <is>
+          <t>https://ku.meirishici.com/book/pmrwx3mbkf
+https://ku.meirishici.com/book/pmrwx3mbkf/cayxnlojjp</t>
+        </is>
+      </c>
+      <c r="G215" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H215" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I215" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J215" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -11592,34 +11630,36 @@
       </c>
     </row>
     <row r="224" ht="116" spans="1:10">
-      <c r="A224" s="11" t="s">
+      <c r="A224" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B224" s="12">
+      <c r="B224" s="16">
         <v>8245</v>
       </c>
-      <c r="C224" s="13" t="s">
+      <c r="C224" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="D224" s="12">
+      <c r="D224" s="16">
         <v>14</v>
       </c>
-      <c r="E224" s="12">
+      <c r="E224" s="16">
         <v>3</v>
       </c>
-      <c r="F224" s="14" t="s">
-        <v>323</v>
-      </c>
-      <c r="G224" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H224" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I224" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J224" s="15" t="s">
+      <c r="F224" s="18" t="inlineStr">
+        <is>
+          <t>https://www.ecsponline.com/yz/BDBABB4B9C8264B28BD9601A2172877C4000.pdf</t>
+        </is>
+      </c>
+      <c r="G224" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H224" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I224" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J224" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -11848,34 +11888,36 @@
       </c>
     </row>
     <row r="232" ht="409.5" spans="1:10">
-      <c r="A232" s="11" t="s">
+      <c r="A232" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B232" s="12">
+      <c r="B232" s="16">
         <v>9269</v>
       </c>
-      <c r="C232" s="13" t="s">
+      <c r="C232" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="D232" s="12">
+      <c r="D232" s="16">
         <v>16</v>
       </c>
-      <c r="E232" s="12">
+      <c r="E232" s="16">
         <v>3</v>
       </c>
-      <c r="F232" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="G232" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H232" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I232" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J232" s="15" t="s">
+      <c r="F232" s="18" t="inlineStr">
+        <is>
+          <t>https://zh.wikisource.org/wiki/山谷集_(四庫全書本)/卷01</t>
+        </is>
+      </c>
+      <c r="G232" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H232" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I232" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J232" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -12424,34 +12466,36 @@
       </c>
     </row>
     <row r="250" ht="130.5" spans="1:10">
-      <c r="A250" s="11" t="s">
+      <c r="A250" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B250" s="12">
+      <c r="B250" s="16">
         <v>11581</v>
       </c>
-      <c r="C250" s="13" t="s">
+      <c r="C250" s="17" t="s">
         <v>360</v>
       </c>
-      <c r="D250" s="12">
+      <c r="D250" s="16">
         <v>19</v>
       </c>
-      <c r="E250" s="12">
+      <c r="E250" s="16">
         <v>1</v>
       </c>
-      <c r="F250" s="14" t="s">
-        <v>361</v>
-      </c>
-      <c r="G250" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H250" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I250" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J250" s="15" t="s">
+      <c r="F250" s="18" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/Category:庫車州鄉土志</t>
+        </is>
+      </c>
+      <c r="G250" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H250" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I250" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J250" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -12712,34 +12756,36 @@
       </c>
     </row>
     <row r="259" ht="87" spans="1:10">
-      <c r="A259" s="11" t="s">
+      <c r="A259" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B259" s="12">
+      <c r="B259" s="16">
         <v>12734</v>
       </c>
-      <c r="C259" s="13" t="s">
+      <c r="C259" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="D259" s="12">
+      <c r="D259" s="16">
         <v>21</v>
       </c>
-      <c r="E259" s="12">
+      <c r="E259" s="16">
         <v>1</v>
       </c>
-      <c r="F259" s="14" t="s">
-        <v>372</v>
-      </c>
-      <c r="G259" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H259" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I259" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J259" s="15" t="s">
+      <c r="F259" s="18" t="inlineStr">
+        <is>
+          <t>https://ygx.sxu.edu.cn/db/期刊/20230419/25163_山西玄中寺八思巴字蒙古语圣旨碑杂考.pdf</t>
+        </is>
+      </c>
+      <c r="G259" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H259" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I259" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J259" s="19" t="s">
         <v>18</v>
       </c>
     </row>

--- a/姜博文爬虫自查结果.xlsx
+++ b/姜博文爬虫自查结果.xlsx
@@ -794,10 +794,7 @@
     <t>《光绪永昌府志》</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File%3A%EF%BC%88%E5%85%89%E7%B7%92%EF%BC%89%E6%B0%B8%E6%98%8C%E5%BA%9C%E5%BF%97_-_%E5%85%89%E7%B7%92%E5%8D%81%E4%B8%80%E5%B9%B4_%281885%29.pdf
-https://www.gujishoucang.com/4571.html
-https://www.100fc.com/4190.html
-https://www.xianzhidaquan.com/product.php?id=2785</t>
+    <t>https://commons.wikimedia.org/wiki/File:（光緒）永昌府志_-_光緒十一年_(1885).pdf</t>
   </si>
   <si>
     <t>《石头录》</t>
@@ -823,25 +820,19 @@
     <t>《约章成案汇览》</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/Category%3A%E7%B4%84%E7%AB%A0%E6%88%90%E6%A1%88%E5%8C%AF%E8%A6%BD%E4%B9%99%E7%AF%87</t>
+    <t>https://commons.wikimedia.org/wiki/File:CADAL02090185_約章成案匯覽（三十七）.djvu</t>
   </si>
   <si>
     <t>《嘉兴县志》</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File%3ANLC403-312001079985-79683_%E5%98%89%E8%88%88%E7%B8%A3%E8%AA%8C_%E6%B8%85%E5%85%89%E7%B7%9234%E5%B9%B4%281908%29_%E5%8D%B7%E4%B8%80%E5%8D%81%E4%B8%89.pdf
-https://commons.wikimedia.org/wiki/File%3A%EF%BC%88%E5%85%89%E7%B7%92%EF%BC%89%E5%98%89%E8%88%88%E7%B8%A3%E5%BF%97_-_%E5%85%89%E7%B7%92%E4%B8%89%E5%8D%81%E5%9B%9B%E5%B9%B4_%281908%29_-_%E5%8D%B700-16.pdf
-https://commons.wikimedia.org/wiki/File%3A%EF%BC%88%E5%BA%B7%E7%86%99%EF%BC%89%E5%98%89%E8%88%88%E7%B8%A3%E5%BF%97_-_%E5%BA%B7%E7%86%99%E4%BA%8C%E5%8D%81%E5%9B%9B%E5%B9%B4_%281685%29_-_%E5%8D%B77-9.pdf
-https://commons.wikimedia.org/wiki/File%3AGGZBCK095_%E5%98%89%E8%88%88%E7%B8%A3%E5%BF%97.pdf</t>
+    <t>https://commons.wikimedia.org/wiki/File:（光緒）嘉興縣志_-_光緒三十四年_(1908)_-_卷00-16.pdf</t>
   </si>
   <si>
     <t>《汾西县志》</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File%3ANLC892-412000013874-5769_%E5%BA%B7%E7%86%99%E6%B1%BE%E8%A5%BF%E7%B8%A3%E8%AA%8C_%E7%AC%AC1%E5%86%8A.pdf
-https://commons.wikimedia.org/wiki/File%3ANLC403-312001067965-5513_%E6%B1%BE%E8%A5%BF%E7%B8%A3%E8%AA%8C_%E6%B8%85%E5%BA%B7%E7%86%9913%E5%B9%B4%281674%29_%E5%8D%B7%E4%B8%89.pdf
-https://commons.wikimedia.org/wiki/File%3AHarvard_drs_49443700_%E6%B1%BE%E8%A5%BF%E7%B8%A3%E5%BF%97_v.2%E5%8D%B7%E4%B8%89-%E5%9B%9B.pdf
-https://commons.wikimedia.org/wiki/File%3A%EF%BC%88%E5%BA%B7%E7%86%99%EF%BC%89%E6%B1%BE%E8%A5%BF%E7%B8%A3%E5%BF%97_-_%E5%BA%B7%E7%86%99%E5%8D%81%E4%B8%89%E5%B9%B4_%281674%29.pdf</t>
+    <t>https://commons.wikimedia.org/wiki/File:（康熙）汾西縣志_-_康熙十三年_(1674).pdf</t>
   </si>
   <si>
     <t>《宁夏固原杨家庄汉墓发掘简报》</t>
@@ -1107,9 +1098,8 @@
     <t>《盛世危言》</t>
   </si>
   <si>
-    <t>https://commons.wikimedia.org/wiki/File%3ANLC892-312002002809-403222_%E7%9B%9B%E4%B8%96%E5%8D%B1%E8%A8%80%E5%85%A8%E7%B7%A8_%E5%8D%81%E5%9B%9B%E5%8D%B7_%E7%AC%AC1%E5%86%8A.pdf
-https://commons.wikimedia.org/wiki/File%3ANLC892-312002002809-403216_%E7%9B%9B%E4%B8%96%E5%8D%B1%E8%A8%80%E5%85%A8%E7%B7%A8_%E5%8D%81%E5%9B%9B%E5%8D%B7_%E7%AC%AC8%E5%86%8A.pdf
-https://commons.wikimedia.org/wiki/File%3ANLC892-312002002809-403218_%E7%9B%9B%E4%B8%96%E5%8D%B1%E8%A8%80%E5%85%A8%E7%B7%A8_%E5%8D%81%E5%9B%9B%E5%8D%B7_%E7%AC%AC5%E5%86%8A.pdf</t>
+    <t>https://ku.meirishici.com/book/pmrwx3mbkf
+https://ku.meirishici.com/book/pmrwx3mbkf/cayxnlojjp</t>
   </si>
   <si>
     <t>《京尘纪游》</t>
@@ -1164,10 +1154,7 @@
     <t>《神木大保当汉代城址与墓葬考古报告》</t>
   </si>
   <si>
-    <t>https://ci.nii.ac.jp/ncid/BA55296089
-https://ndlsearch.ndl.go.jp/en/books/R100000002-Ia1000059290
-https://ndlsearch.ndl.go.jp/books/R100000002-Ia1000059290
-https://www.ecsponline.com/yz/BDBABB4B9C8264B28BD9601A2172877C4000.pdf</t>
+    <t>https://www.ecsponline.com/yz/BDBABB4B9C8264B28BD9601A2172877C4000.pdf</t>
   </si>
   <si>
     <t>《陕西咸阳底张村十六国墓出土陶连枝灯》</t>
@@ -1210,106 +1197,7 @@
     <t>《山谷集》</t>
   </si>
   <si>
-    <t>https://ndlsearch.ndl.go.jp/books/R100000002-I000000751605
-https://zh.wikisource.org/zh-hant/%E5%B1%B1%E8%B0%B7%E9%9B%86_%28%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC%29/%E5%B9%B4%E8%AD%9C%E5%8D%B715
-https://zh.wikisource.org/zh-hant/%E5%B1%B1%E8%B0%B7%E9%9B%86_%28%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC%29/%E5%B9%B4%E8%AD%9C%E5%8D%B724
-https://zh.wikisource.org/zh-hant/%E5%B1%B1%E8%B0%B7%E9%9B%86_%28%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC%29/%E5%B9%B4%E8%AD%9C%E5%8D%B710
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B704
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B702
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B701
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B703
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B707
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B705
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B706
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B709
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B708
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B711
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B710
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B713
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B715
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B712
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B714
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B716
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B719
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B717
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B718
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B720
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B722
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B723
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B724
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B721
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B725
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B726
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B727
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B729
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B728
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%8D%B730
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B703
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B702
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B701
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B704
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B707
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B705
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B708
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B710
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B709
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B711
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B713
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B714
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B712
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B701
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B702
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%A4%96%E9%9B%86%E5%8D%B706
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B703
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B706
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B707
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B705
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B704
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B708
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B710
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B709
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B711
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B713
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B714
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B712
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B715
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B716
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B717
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B719
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B718
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%88%AB%E9%9B%86%E5%8D%B720
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E7%B0%A1%E5%B0%BA%E5%8D%B7%E4%B8%8B
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B701
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E7%B0%A1%E5%B0%BA%E5%8D%B7%E4%B8%8A
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B702
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B704
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B703
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B706
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B705
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B707
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B709
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B710
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B708
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B713
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B712
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B714
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B711
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B715
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B716
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B718
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B717
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B719
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B722
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B721
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B723
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B720
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B724
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B726
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B725
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B727
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B730
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B729
-https://zh.wikisource.org/wiki/%E5%B1%B1%E8%B0%B7%E9%9B%86_(%E5%9B%9B%E5%BA%AB%E5%85%A8%E6%9B%B8%E6%9C%AC)/%E5%B9%B4%E8%AD%9C%E5%8D%B728</t>
+    <t>https://zh.wikisource.org/wiki/山谷集_(四庫全書本)/卷01</t>
   </si>
   <si>
     <t>《关于缴送吴光祖边区特种民族证明书并核列为特别生费的呈、函、代电》</t>
@@ -1392,10 +1280,7 @@
     <t>《库车直隶州乡土志》</t>
   </si>
   <si>
-    <t>https://www.qnfz.com/news/xiazai/2238.html
-https://qnfz.com/m/news/xiazai/2238.html
-https://www.clc86.com/down/4441
-https://commons.wikimedia.org/wiki/Category%3A%E5%BA%AB%E8%BB%8A%E5%B7%9E%E9%84%89%E5%9C%9F%E5%BF%97</t>
+    <t>https://commons.wikimedia.org/wiki/Category:庫車州鄉土志</t>
   </si>
   <si>
     <t>《奏为审明新疆昌吉县商民许世二扎毙监生贺福详案按律定拟事》</t>
@@ -1429,9 +1314,7 @@
     <t>《忽必烈皇帝牛年圣旨碑》</t>
   </si>
   <si>
-    <t>https://shop.kongfz.com/151391/cat_57/
-https://www.sinoss.net/uploadfile/2012/0615/20120615100319369.pdf
-https://dokumen.pub/9787531152330.html</t>
+    <t>https://ygx.sxu.edu.cn/db/期刊/20230419/25163_山西玄中寺八思巴字蒙古语圣旨碑杂考.pdf</t>
   </si>
   <si>
     <t>《蒙藏会议预备会阎在太原召集》</t>
@@ -10050,7 +9933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" ht="174" spans="1:10">
+    <row r="175" ht="43.5" spans="1:10">
       <c r="A175" s="11" t="s">
         <v>212</v>
       </c>
@@ -10066,10 +9949,8 @@
       <c r="E175" s="16">
         <v>2</v>
       </c>
-      <c r="F175" s="18" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:（光緒）永昌府志_-_光緒十一年_(1885).pdf</t>
-        </is>
+      <c r="F175" s="18" t="s">
+        <v>242</v>
       </c>
       <c r="G175" s="18" t="s">
         <v>43</v>
@@ -10180,7 +10061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" ht="72.5" spans="1:10">
+    <row r="179" ht="43.5" spans="1:10">
       <c r="A179" s="20" t="s">
         <v>212</v>
       </c>
@@ -10196,10 +10077,8 @@
       <c r="E179" s="16">
         <v>3</v>
       </c>
-      <c r="F179" s="18" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:CADAL02090185_約章成案匯覽（三十七）.djvu</t>
-        </is>
+      <c r="F179" s="18" t="s">
+        <v>249</v>
       </c>
       <c r="G179" s="18" t="s">
         <v>43</v>
@@ -10214,7 +10093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="180" ht="377" spans="1:10">
+    <row r="180" ht="43.5" spans="1:10">
       <c r="A180" s="20" t="s">
         <v>212</v>
       </c>
@@ -10230,10 +10109,8 @@
       <c r="E180" s="16">
         <v>3</v>
       </c>
-      <c r="F180" s="18" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:（光緒）嘉興縣志_-_光緒三十四年_(1908)_-_卷00-16.pdf</t>
-        </is>
+      <c r="F180" s="18" t="s">
+        <v>251</v>
       </c>
       <c r="G180" s="18" t="s">
         <v>43</v>
@@ -10248,7 +10125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="181" ht="362.5" spans="1:10">
+    <row r="181" ht="43.5" spans="1:10">
       <c r="A181" s="20" t="s">
         <v>212</v>
       </c>
@@ -10264,10 +10141,8 @@
       <c r="E181" s="16">
         <v>3</v>
       </c>
-      <c r="F181" s="18" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:（康熙）汾西縣志_-_康熙十三年_(1674).pdf</t>
-        </is>
+      <c r="F181" s="18" t="s">
+        <v>253</v>
       </c>
       <c r="G181" s="18" t="s">
         <v>43</v>
@@ -10507,34 +10382,34 @@
       </c>
     </row>
     <row r="189" ht="16.5" spans="1:10">
-      <c r="A189" s="6" t="s">
+      <c r="A189" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B189" s="7">
+      <c r="B189" s="16">
         <v>3759</v>
       </c>
-      <c r="C189" s="8" t="s">
+      <c r="C189" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="D189" s="7">
+      <c r="D189" s="16">
         <v>7</v>
       </c>
-      <c r="E189" s="7">
+      <c r="E189" s="16">
         <v>1</v>
       </c>
-      <c r="F189" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G189" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H189" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I189" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J189" s="10" t="s">
+      <c r="F189" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G189" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H189" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J189" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -10955,34 +10830,34 @@
       </c>
     </row>
     <row r="203" ht="29" spans="1:10">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B203" s="12">
+      <c r="B203" s="16">
         <v>5556</v>
       </c>
-      <c r="C203" s="13" t="s">
+      <c r="C203" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="D203" s="12">
+      <c r="D203" s="16">
         <v>9</v>
       </c>
-      <c r="E203" s="12">
+      <c r="E203" s="16">
         <v>3</v>
       </c>
-      <c r="F203" s="14" t="s">
+      <c r="F203" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="G203" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H203" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I203" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J203" s="15" t="s">
+      <c r="G203" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H203" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I203" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J203" s="19" t="s">
         <v>18</v>
       </c>
     </row>
@@ -11147,34 +11022,34 @@
       </c>
     </row>
     <row r="209" ht="16.5" spans="1:10">
-      <c r="A209" s="6" t="s">
+      <c r="A209" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B209" s="7">
+      <c r="B209" s="16">
         <v>6324</v>
       </c>
-      <c r="C209" s="8" t="s">
+      <c r="C209" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="D209" s="7">
+      <c r="D209" s="16">
         <v>11</v>
       </c>
-      <c r="E209" s="7">
+      <c r="E209" s="16">
         <v>1</v>
       </c>
-      <c r="F209" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G209" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H209" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I209" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J209" s="10" t="s">
+      <c r="F209" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G209" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H209" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I209" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J209" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -11338,7 +11213,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="215" ht="304.5" spans="1:10">
+    <row r="215" ht="58" spans="1:10">
       <c r="A215" s="20" t="s">
         <v>212</v>
       </c>
@@ -11354,11 +11229,8 @@
       <c r="E215" s="16">
         <v>3</v>
       </c>
-      <c r="F215" s="18" t="inlineStr">
-        <is>
-          <t>https://ku.meirishici.com/book/pmrwx3mbkf
-https://ku.meirishici.com/book/pmrwx3mbkf/cayxnlojjp</t>
-        </is>
+      <c r="F215" s="18" t="s">
+        <v>308</v>
       </c>
       <c r="G215" s="18" t="s">
         <v>43</v>
@@ -11629,7 +11501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" ht="116" spans="1:10">
+    <row r="224" ht="43.5" spans="1:10">
       <c r="A224" s="20" t="s">
         <v>212</v>
       </c>
@@ -11645,10 +11517,8 @@
       <c r="E224" s="16">
         <v>3</v>
       </c>
-      <c r="F224" s="18" t="inlineStr">
-        <is>
-          <t>https://www.ecsponline.com/yz/BDBABB4B9C8264B28BD9601A2172877C4000.pdf</t>
-        </is>
+      <c r="F224" s="18" t="s">
+        <v>323</v>
       </c>
       <c r="G224" s="18" t="s">
         <v>43</v>
@@ -11824,34 +11694,34 @@
       </c>
     </row>
     <row r="230" ht="16.5" spans="1:10">
-      <c r="A230" s="6" t="s">
+      <c r="A230" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B230" s="7">
+      <c r="B230" s="16">
         <v>9013</v>
       </c>
-      <c r="C230" s="8" t="s">
+      <c r="C230" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="D230" s="7">
+      <c r="D230" s="16">
         <v>15</v>
       </c>
-      <c r="E230" s="7">
+      <c r="E230" s="16">
         <v>1</v>
       </c>
-      <c r="F230" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G230" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H230" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I230" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J230" s="10" t="s">
+      <c r="F230" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G230" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H230" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I230" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J230" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -11887,7 +11757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" ht="409.5" spans="1:10">
+    <row r="232" ht="29" spans="1:10">
       <c r="A232" s="20" t="s">
         <v>212</v>
       </c>
@@ -11903,10 +11773,8 @@
       <c r="E232" s="16">
         <v>3</v>
       </c>
-      <c r="F232" s="18" t="inlineStr">
-        <is>
-          <t>https://zh.wikisource.org/wiki/山谷集_(四庫全書本)/卷01</t>
-        </is>
+      <c r="F232" s="18" t="s">
+        <v>336</v>
       </c>
       <c r="G232" s="18" t="s">
         <v>43</v>
@@ -12050,34 +11918,34 @@
       </c>
     </row>
     <row r="237" ht="16.5" spans="1:10">
-      <c r="A237" s="6" t="s">
+      <c r="A237" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B237" s="7">
+      <c r="B237" s="16">
         <v>9911</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="17" t="s">
         <v>343</v>
       </c>
-      <c r="D237" s="7">
-        <v>17</v>
-      </c>
-      <c r="E237" s="7">
+      <c r="D237" s="16">
+        <v>17</v>
+      </c>
+      <c r="E237" s="16">
         <v>1</v>
       </c>
-      <c r="F237" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G237" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H237" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I237" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J237" s="10" t="s">
+      <c r="F237" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G237" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H237" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I237" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J237" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -12274,34 +12142,34 @@
       </c>
     </row>
     <row r="244" ht="16.5" spans="1:10">
-      <c r="A244" s="6" t="s">
+      <c r="A244" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B244" s="7">
+      <c r="B244" s="16">
         <v>10808</v>
       </c>
-      <c r="C244" s="8" t="s">
+      <c r="C244" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="D244" s="7">
-        <v>18</v>
-      </c>
-      <c r="E244" s="7">
+      <c r="D244" s="16">
+        <v>18</v>
+      </c>
+      <c r="E244" s="16">
         <v>3</v>
       </c>
-      <c r="F244" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G244" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="H244" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I244" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J244" s="10" t="s">
+      <c r="F244" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G244" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="H244" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I244" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J244" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -12465,7 +12333,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="250" ht="130.5" spans="1:10">
+    <row r="250" ht="29" spans="1:10">
       <c r="A250" s="20" t="s">
         <v>212</v>
       </c>
@@ -12481,10 +12349,8 @@
       <c r="E250" s="16">
         <v>1</v>
       </c>
-      <c r="F250" s="18" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/Category:庫車州鄉土志</t>
-        </is>
+      <c r="F250" s="18" t="s">
+        <v>361</v>
       </c>
       <c r="G250" s="18" t="s">
         <v>43</v>
@@ -12755,7 +12621,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="259" ht="87" spans="1:10">
+    <row r="259" ht="43.5" spans="1:10">
       <c r="A259" s="20" t="s">
         <v>212</v>
       </c>
@@ -12771,10 +12637,8 @@
       <c r="E259" s="16">
         <v>1</v>
       </c>
-      <c r="F259" s="18" t="inlineStr">
-        <is>
-          <t>https://ygx.sxu.edu.cn/db/期刊/20230419/25163_山西玄中寺八思巴字蒙古语圣旨碑杂考.pdf</t>
-        </is>
+      <c r="F259" s="18" t="s">
+        <v>372</v>
       </c>
       <c r="G259" s="18" t="s">
         <v>43</v>
